--- a/ver2/tree.xlsx
+++ b/ver2/tree.xlsx
@@ -5,19 +5,19 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mini\Documents\25\project\tree\м2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\i7\drevo\4\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="27300" windowHeight="9585"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="27300" windowHeight="9585" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="person" sheetId="1" r:id="rId1"/>
     <sheet name="family" sheetId="2" r:id="rId2"/>
-    <sheet name="foto_family" sheetId="4" r:id="rId3"/>
-    <sheet name="Лист1" sheetId="6" r:id="rId4"/>
-    <sheet name="tag" sheetId="3" r:id="rId5"/>
-    <sheet name="file" sheetId="5" r:id="rId6"/>
+    <sheet name="foto_person" sheetId="6" r:id="rId3"/>
+    <sheet name="foto_family" sheetId="4" r:id="rId4"/>
+    <sheet name="foto_group" sheetId="5" r:id="rId5"/>
+    <sheet name="tag" sheetId="3" r:id="rId6"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -29,10 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="66">
-  <si>
-    <t>label</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="75">
   <si>
     <t>sex</t>
   </si>
@@ -163,9 +160,6 @@
     <t>Семья Ульяновых</t>
   </si>
   <si>
-    <t xml:space="preserve">Слева направо: стоят – Ольга, Александр, Анна; сидят – Мария Александровна с младшей дочерью Марией, Дмитрий, Илья Николаевич, Владимир. </t>
-  </si>
-  <si>
     <t>Симбирск</t>
   </si>
   <si>
@@ -227,13 +221,46 @@
   </si>
   <si>
     <t>jpg</t>
+  </si>
+  <si>
+    <t>Ульянов_Владимир_Ильич</t>
+  </si>
+  <si>
+    <t>Рабочий кабинет</t>
+  </si>
+  <si>
+    <t>7.10.1922</t>
+  </si>
+  <si>
+    <t>https://maysuryan.livejournal.com/2664904.html</t>
+  </si>
+  <si>
+    <t>id_person</t>
+  </si>
+  <si>
+    <t>7.11.2018</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Ленин и Свердлов на Красной площади, во время открытия временного памятника Карлу Марксу</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Ленин и Свердлов на Красной площади</t>
+  </si>
+  <si>
+    <t>Красная площадь</t>
+  </si>
+  <si>
+    <t>id_personAll</t>
+  </si>
+  <si>
+    <t>Слева направо: стоят – Ольга, Александр, Анна; сидят – Мария Александровна с младшей дочерью Марией, Дмитрий, Илья Николаевич, Владимир</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -268,6 +295,14 @@
       <family val="1"/>
       <charset val="204"/>
     </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color rgb="FF242F33"/>
+      <name val="Georgia"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -290,7 +325,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -299,6 +334,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
@@ -600,46 +639,46 @@
   <sheetData>
     <row r="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="I1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>61</v>
-      </c>
       <c r="K1" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -648,34 +687,34 @@
         <v>Ульянов_Владимир_Ильич</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E2" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>18</v>
-      </c>
       <c r="G2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="J2" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="K2" s="2" t="s">
         <v>62</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -684,28 +723,28 @@
         <v>Ульянов_Илья_Николаевич</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E3" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>20</v>
-      </c>
       <c r="G3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="J3" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -714,29 +753,29 @@
         <v>Бланк_Мария_Александровна</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E4" s="3"/>
       <c r="G4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="J4" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="I4" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>26</v>
-      </c>
       <c r="K4" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -745,23 +784,23 @@
         <v>Ульянин_Николай_Васильевич</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>14</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>15</v>
       </c>
       <c r="E5" s="3"/>
       <c r="G5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="J5" s="2" t="s">
         <v>27</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -770,22 +809,22 @@
         <v>Смирнова_Анна_Алексеевна</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="J6" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -834,31 +873,31 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="D1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>58</v>
-      </c>
       <c r="I1" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -867,13 +906,13 @@
         <v>Ульянов_Илья_Николаевич-Бланк_Мария_Александровна</v>
       </c>
       <c r="B2" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
         <v>17</v>
       </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
       <c r="D2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -889,12 +928,157 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:I25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="28.5703125" customWidth="1"/>
+    <col min="2" max="2" width="11.7109375" customWidth="1"/>
+    <col min="3" max="3" width="15" customWidth="1"/>
+    <col min="4" max="4" width="34.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21" customWidth="1"/>
+    <col min="9" max="9" width="16.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B2">
+        <v>1922</v>
+      </c>
+      <c r="C2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D2" t="str">
+        <f>A2&amp;"-"&amp;B2&amp;"."&amp;C2</f>
+        <v>Ульянов_Владимир_Ильич-1922.jpg</v>
+      </c>
+      <c r="E2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="I2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G3" s="2"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G4" s="2"/>
+    </row>
+    <row r="5" spans="1:9" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="F5" s="8"/>
+      <c r="G5" s="2"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G6" s="2"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G7" s="2"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G8" s="2"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G9" s="2"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G10" s="2"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G11" s="2"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G12" s="2"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G13" s="2"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G14" s="2"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G15" s="2"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G16" s="2"/>
+    </row>
+    <row r="17" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G17" s="2"/>
+    </row>
+    <row r="18" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G18" s="2"/>
+    </row>
+    <row r="19" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G19" s="2"/>
+    </row>
+    <row r="20" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G20" s="2"/>
+    </row>
+    <row r="21" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G21" s="2"/>
+    </row>
+    <row r="22" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G22" s="2"/>
+    </row>
+    <row r="23" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G23" s="2"/>
+    </row>
+    <row r="24" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G24" s="2"/>
+    </row>
+    <row r="25" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G25" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:M20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="55.140625" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="5.42578125" customWidth="1"/>
+    <col min="3" max="3" width="13.28515625" customWidth="1"/>
     <col min="4" max="4" width="62.85546875" customWidth="1"/>
     <col min="5" max="5" width="21.7109375" customWidth="1"/>
     <col min="6" max="6" width="5.85546875" customWidth="1"/>
@@ -908,77 +1092,129 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B2">
         <v>1879</v>
       </c>
       <c r="C2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D2" t="str">
         <f>A2&amp;"-"&amp;B2&amp;"."&amp;C2</f>
         <v>Ульянов_Илья_Николаевич-Бланк_Мария_Александровна-1879.jpg</v>
       </c>
       <c r="E2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I2" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="I2" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="J2">
+      <c r="J2" s="2">
         <v>1879</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
+        <v>74</v>
+      </c>
+      <c r="M2" t="s">
         <v>44</v>
       </c>
-      <c r="M2" t="s">
-        <v>46</v>
-      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J3" s="2"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J4" s="2"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J5" s="2"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J6" s="2"/>
     </row>
     <row r="7" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="E7" s="7"/>
+      <c r="J7" s="2"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J8" s="2"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J9" s="2"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J10" s="2"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J11" s="2"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J12" s="2"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J13" s="2"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J14" s="2"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J15" s="2"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J16" s="2"/>
+    </row>
+    <row r="17" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J17" s="2"/>
+    </row>
+    <row r="18" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J18" s="2"/>
+    </row>
+    <row r="19" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J19" s="2"/>
+    </row>
+    <row r="20" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J20" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -986,20 +1222,151 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="27.7109375" customWidth="1"/>
+    <col min="2" max="2" width="14.28515625" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" customWidth="1"/>
+    <col min="4" max="4" width="35.5703125" customWidth="1"/>
+    <col min="5" max="5" width="36.42578125" customWidth="1"/>
+    <col min="6" max="6" width="29.85546875" customWidth="1"/>
+    <col min="7" max="7" width="11.7109375" customWidth="1"/>
+    <col min="9" max="9" width="15.7109375" customWidth="1"/>
+    <col min="10" max="10" width="32.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B2">
+        <v>1922</v>
+      </c>
+      <c r="C2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D2" t="str">
+        <f>A2&amp;"-"&amp;B2&amp;"."&amp;C2</f>
+        <v>Ульянов_Владимир_Ильич-1922.jpg</v>
+      </c>
+      <c r="E2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="J2" t="s">
+        <v>70</v>
+      </c>
+      <c r="K2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H3" s="2"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H4" s="2"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H5" s="2"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H6" s="2"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H7" s="2"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H8" s="2"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H9" s="2"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H10" s="2"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H11" s="2"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H12" s="2"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H13" s="2"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H14" s="2"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H15" s="2"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H16" s="2"/>
+    </row>
+    <row r="17" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H17" s="2"/>
+    </row>
+    <row r="18" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H18" s="2"/>
+    </row>
+    <row r="19" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H19" s="2"/>
+    </row>
+    <row r="20" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H20" s="2"/>
+    </row>
+    <row r="21" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H21" s="2"/>
+    </row>
+    <row r="22" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H22" s="2"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/ver2/tree.xlsx
+++ b/ver2/tree.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="27300" windowHeight="9585" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="27300" windowHeight="9585" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="person" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="80">
   <si>
     <t>sex</t>
   </si>
@@ -254,6 +254,21 @@
   </si>
   <si>
     <t>Слева направо: стоят – Ольга, Александр, Анна; сидят – Мария Александровна с младшей дочерью Марией, Дмитрий, Илья Николаевич, Владимир</t>
+  </si>
+  <si>
+    <t>Свердлов_Яков_Михайлович</t>
+  </si>
+  <si>
+    <t>В.И. Ленин, Я.М. Свердлов, В.А. Аванесов, Н.И. Подвойский, Г.И. Окулова и М.Ф. Владимирский перед открытой мемориальной доской в память павших за мир и братство народов. Панно «Павшим в борьбе за мир и братство народов». Скульптор Сергей Конёнков. Установлено в 1918 году. Демонтировано в 1948 году.</t>
+  </si>
+  <si>
+    <t>Москва</t>
+  </si>
+  <si>
+    <t>Панно «Павшим в борьбе за мир и братство народов».</t>
+  </si>
+  <si>
+    <t>Свердлов_Яков_Михайлович; Ульянов_Владимир_Ильич</t>
   </si>
 </sst>
 </file>
@@ -325,7 +340,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -338,6 +353,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
@@ -1224,7 +1242,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.7109375" customWidth="1"/>
@@ -1232,7 +1250,7 @@
     <col min="3" max="3" width="12.140625" customWidth="1"/>
     <col min="4" max="4" width="35.5703125" customWidth="1"/>
     <col min="5" max="5" width="36.42578125" customWidth="1"/>
-    <col min="6" max="6" width="29.85546875" customWidth="1"/>
+    <col min="6" max="6" width="54" customWidth="1"/>
     <col min="7" max="7" width="11.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" customWidth="1"/>
     <col min="10" max="10" width="32.85546875" customWidth="1"/>
@@ -1278,14 +1296,14 @@
         <v>64</v>
       </c>
       <c r="B2">
-        <v>1922</v>
+        <v>1918</v>
       </c>
       <c r="C2" t="s">
         <v>63</v>
       </c>
       <c r="D2" t="str">
         <f>A2&amp;"-"&amp;B2&amp;"."&amp;C2</f>
-        <v>Ульянов_Владимир_Ильич-1922.jpg</v>
+        <v>Ульянов_Владимир_Ильич-1918.jpg</v>
       </c>
       <c r="E2" t="s">
         <v>71</v>
@@ -1306,8 +1324,38 @@
         <v>67</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="H3" s="2"/>
+    <row r="3" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="B3">
+        <v>1918</v>
+      </c>
+      <c r="C3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D3" t="str">
+        <f>A3&amp;"-"&amp;B3&amp;"."&amp;C3</f>
+        <v>Свердлов_Яков_Михайлович-1918.jpg</v>
+      </c>
+      <c r="E3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F3" t="s">
+        <v>79</v>
+      </c>
+      <c r="G3" t="s">
+        <v>77</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="J3" t="s">
+        <v>76</v>
+      </c>
+      <c r="K3" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="H4" s="2"/>
@@ -1363,11 +1411,12 @@
     <row r="21" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H21" s="2"/>
     </row>
-    <row r="22" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H22" s="2"/>
-    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A3" r:id="rId1" display="https://revo.kemrsl.ru/?p=520"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
 </worksheet>
 </file>
 

--- a/ver2/tree.xlsx
+++ b/ver2/tree.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="27300" windowHeight="9585" activeTab="4"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="27300" windowHeight="9585" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="person" sheetId="1" r:id="rId1"/>
@@ -17,7 +17,9 @@
     <sheet name="foto_person" sheetId="6" r:id="rId3"/>
     <sheet name="foto_family" sheetId="4" r:id="rId4"/>
     <sheet name="foto_group" sheetId="5" r:id="rId5"/>
-    <sheet name="tag" sheetId="3" r:id="rId6"/>
+    <sheet name="foto_location" sheetId="7" r:id="rId6"/>
+    <sheet name="event" sheetId="8" r:id="rId7"/>
+    <sheet name="tag" sheetId="3" r:id="rId8"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -29,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="94">
   <si>
     <t>sex</t>
   </si>
@@ -269,13 +271,55 @@
   </si>
   <si>
     <t>Свердлов_Яков_Михайлович; Ульянов_Владимир_Ильич</t>
+  </si>
+  <si>
+    <t>id_loc</t>
+  </si>
+  <si>
+    <t>synonym_</t>
+  </si>
+  <si>
+    <t>Ульяновск, ул. Ленина 70</t>
+  </si>
+  <si>
+    <t>2020хх</t>
+  </si>
+  <si>
+    <t>png</t>
+  </si>
+  <si>
+    <t>Ульянов_Владимир_Ильич; Ульянов_Илья_Николаевич</t>
+  </si>
+  <si>
+    <t>id_familyAll</t>
+  </si>
+  <si>
+    <t>id_event</t>
+  </si>
+  <si>
+    <t>foto_person</t>
+  </si>
+  <si>
+    <t>eventGroup</t>
+  </si>
+  <si>
+    <t>foto_family</t>
+  </si>
+  <si>
+    <t>foto_location</t>
+  </si>
+  <si>
+    <t>locationGroup</t>
+  </si>
+  <si>
+    <t>Ульяновск_ Ленина_70</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -318,6 +362,13 @@
       <family val="1"/>
       <charset val="204"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -340,7 +391,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -356,6 +407,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
@@ -1091,7 +1143,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:N20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="55.140625" customWidth="1"/>
@@ -1108,7 +1160,7 @@
     <col min="13" max="13" width="13.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>37</v>
       </c>
@@ -1148,8 +1200,11 @@
       <c r="M1" s="1" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N1" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>36</v>
       </c>
@@ -1179,47 +1234,47 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="J3" s="2"/>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="J4" s="2"/>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="J5" s="2"/>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="J6" s="2"/>
     </row>
-    <row r="7" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="E7" s="7"/>
       <c r="J7" s="2"/>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="J8" s="2"/>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="J9" s="2"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="J10" s="2"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="J11" s="2"/>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="J12" s="2"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="J13" s="2"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="J14" s="2"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="J15" s="2"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="J16" s="2"/>
     </row>
     <row r="17" spans="10:10" x14ac:dyDescent="0.25">
@@ -1422,6 +1477,172 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="25.5703125" customWidth="1"/>
+    <col min="2" max="2" width="16.5703125" customWidth="1"/>
+    <col min="3" max="3" width="16.140625" customWidth="1"/>
+    <col min="4" max="4" width="34.42578125" customWidth="1"/>
+    <col min="5" max="6" width="25" customWidth="1"/>
+    <col min="7" max="7" width="39.28515625" customWidth="1"/>
+    <col min="8" max="8" width="47.140625" customWidth="1"/>
+    <col min="9" max="9" width="16.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.28515625" customWidth="1"/>
+    <col min="12" max="12" width="16" customWidth="1"/>
+    <col min="13" max="13" width="12.28515625" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D2" t="str">
+        <f>A2&amp;"-"&amp;B2&amp;"."&amp;C2</f>
+        <v>Ульяновск_ Ленина_70-2020хх.png</v>
+      </c>
+      <c r="E2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G2" t="s">
+        <v>85</v>
+      </c>
+      <c r="H2" t="s">
+        <v>36</v>
+      </c>
+      <c r="I2" t="s">
+        <v>82</v>
+      </c>
+      <c r="L2" s="11"/>
+      <c r="N2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:M1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="13.42578125" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="16.28515625" customWidth="1"/>
+    <col min="6" max="6" width="12.7109375" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" customWidth="1"/>
+    <col min="10" max="10" width="14.140625" customWidth="1"/>
+    <col min="11" max="11" width="18.140625" customWidth="1"/>
+    <col min="12" max="12" width="16" customWidth="1"/>
+    <col min="13" max="13" width="26.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>

--- a/ver2/tree.xlsx
+++ b/ver2/tree.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="27300" windowHeight="9585" activeTab="5"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="27300" windowHeight="9585" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="person" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="foto_group" sheetId="5" r:id="rId5"/>
     <sheet name="foto_location" sheetId="7" r:id="rId6"/>
     <sheet name="event" sheetId="8" r:id="rId7"/>
-    <sheet name="tag" sheetId="3" r:id="rId8"/>
+    <sheet name="language" sheetId="3" r:id="rId8"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="135">
   <si>
     <t>sex</t>
   </si>
@@ -183,9 +183,6 @@
     <t>date_</t>
   </si>
   <si>
-    <t>person_label_</t>
-  </si>
-  <si>
     <t>hyperLink_</t>
   </si>
   <si>
@@ -313,6 +310,132 @@
   </si>
   <si>
     <t>Ульяновск_ Ленина_70</t>
+  </si>
+  <si>
+    <t>object</t>
+  </si>
+  <si>
+    <t>sheet</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>ru</t>
+  </si>
+  <si>
+    <t>en</t>
+  </si>
+  <si>
+    <t>person</t>
+  </si>
+  <si>
+    <t>ФИО</t>
+  </si>
+  <si>
+    <t>родился</t>
+  </si>
+  <si>
+    <t>умер</t>
+  </si>
+  <si>
+    <t>ссылка</t>
+  </si>
+  <si>
+    <t>family</t>
+  </si>
+  <si>
+    <t>союз</t>
+  </si>
+  <si>
+    <t>место</t>
+  </si>
+  <si>
+    <t>переименован</t>
+  </si>
+  <si>
+    <t>описание</t>
+  </si>
+  <si>
+    <t>suffix</t>
+  </si>
+  <si>
+    <t>название</t>
+  </si>
+  <si>
+    <t>дата</t>
+  </si>
+  <si>
+    <t>person_label</t>
+  </si>
+  <si>
+    <t>foto_group</t>
+  </si>
+  <si>
+    <t>синоним</t>
+  </si>
+  <si>
+    <t>renamed</t>
+  </si>
+  <si>
+    <t>full name</t>
+  </si>
+  <si>
+    <t>born</t>
+  </si>
+  <si>
+    <t>died</t>
+  </si>
+  <si>
+    <t>link</t>
+  </si>
+  <si>
+    <t>union</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>label</t>
+  </si>
+  <si>
+    <t>title</t>
+  </si>
+  <si>
+    <t>date</t>
+  </si>
+  <si>
+    <t>synonym</t>
+  </si>
+  <si>
+    <t>event</t>
+  </si>
+  <si>
+    <t>Открытие Панно «Павшим в борьбе за мир и братство народов»</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Открытие_Панно </t>
+  </si>
+  <si>
+    <t>Свердлов_Яков_Михайлович-1918.jpg</t>
+  </si>
+  <si>
+    <t>Ульянов_Владимир_Ильич-1922.jpg</t>
+  </si>
+  <si>
+    <t>«Павшим в борьбе за мир и братство народов»</t>
+  </si>
+  <si>
+    <t>На_Красной_площади</t>
+  </si>
+  <si>
+    <t>Ульянов_Владимир_Ильич-1918.jpg</t>
+  </si>
+  <si>
+    <t>Ульяновск_ Ленина_70-2020хх.png</t>
   </si>
 </sst>
 </file>
@@ -712,13 +835,13 @@
         <v>9</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>1</v>
@@ -730,16 +853,16 @@
         <v>3</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>33</v>
@@ -775,16 +898,16 @@
         <v>20</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J2" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="K2" s="2" t="s">
         <v>61</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -939,6 +1062,9 @@
     <col min="3" max="3" width="39.5703125" customWidth="1"/>
     <col min="4" max="4" width="30" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="7" max="7" width="13.28515625" customWidth="1"/>
+    <col min="8" max="8" width="11" customWidth="1"/>
+    <col min="9" max="9" width="13.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -952,10 +1078,10 @@
         <v>8</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>54</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>55</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>45</v>
@@ -964,10 +1090,10 @@
         <v>46</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -1014,10 +1140,10 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>52</v>
+        <v>109</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>38</v>
@@ -1029,40 +1155,40 @@
         <v>48</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B2">
         <v>1922</v>
       </c>
       <c r="C2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D2" t="str">
         <f>A2&amp;"-"&amp;B2&amp;"."&amp;C2</f>
         <v>Ульянов_Владимир_Ильич-1922.jpg</v>
       </c>
       <c r="E2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="I2" t="s">
         <v>66</v>
-      </c>
-      <c r="I2" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -1156,8 +1282,9 @@
     <col min="8" max="8" width="11.5703125" customWidth="1"/>
     <col min="9" max="10" width="14.140625" customWidth="1"/>
     <col min="11" max="11" width="32.140625" customWidth="1"/>
-    <col min="12" max="12" width="34.140625" customWidth="1"/>
+    <col min="12" max="12" width="30.42578125" customWidth="1"/>
     <col min="13" max="13" width="13.140625" customWidth="1"/>
+    <col min="14" max="14" width="17" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -1165,7 +1292,7 @@
         <v>37</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>38</v>
@@ -1186,22 +1313,22 @@
         <v>41</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>49</v>
       </c>
       <c r="K1" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="L1" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>51</v>
-      </c>
       <c r="N1" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
@@ -1212,7 +1339,7 @@
         <v>1879</v>
       </c>
       <c r="C2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D2" t="str">
         <f>A2&amp;"-"&amp;B2&amp;"."&amp;C2</f>
@@ -1228,10 +1355,13 @@
         <v>1879</v>
       </c>
       <c r="L2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M2" t="s">
         <v>44</v>
+      </c>
+      <c r="N2" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
@@ -1313,10 +1443,10 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>38</v>
@@ -1328,88 +1458,88 @@
         <v>48</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>49</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>50</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B2">
         <v>1918</v>
       </c>
       <c r="C2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D2" t="str">
         <f>A2&amp;"-"&amp;B2&amp;"."&amp;C2</f>
         <v>Ульянов_Владимир_Ильич-1918.jpg</v>
       </c>
       <c r="E2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F2" t="s">
+        <v>63</v>
+      </c>
+      <c r="G2" t="s">
         <v>71</v>
       </c>
-      <c r="F2" t="s">
-        <v>64</v>
-      </c>
-      <c r="G2" t="s">
-        <v>72</v>
-      </c>
       <c r="H2" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="J2" t="s">
         <v>69</v>
       </c>
-      <c r="J2" t="s">
-        <v>70</v>
-      </c>
       <c r="K2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B3">
         <v>1918</v>
       </c>
       <c r="C3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D3" t="str">
         <f>A3&amp;"-"&amp;B3&amp;"."&amp;C3</f>
         <v>Свердлов_Яков_Михайлович-1918.jpg</v>
       </c>
       <c r="E3" t="s">
+        <v>77</v>
+      </c>
+      <c r="F3" t="s">
         <v>78</v>
       </c>
-      <c r="F3" t="s">
-        <v>79</v>
-      </c>
       <c r="G3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -1496,10 +1626,10 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>52</v>
+        <v>109</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>38</v>
@@ -1511,61 +1641,61 @@
         <v>48</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>49</v>
       </c>
       <c r="K1" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="L1" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>51</v>
-      </c>
       <c r="N1" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C2" t="s">
         <v>83</v>
-      </c>
-      <c r="C2" t="s">
-        <v>84</v>
       </c>
       <c r="D2" t="str">
         <f>A2&amp;"-"&amp;B2&amp;"."&amp;C2</f>
         <v>Ульяновск_ Ленина_70-2020хх.png</v>
       </c>
       <c r="E2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F2" t="s">
         <v>43</v>
       </c>
       <c r="G2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H2" t="s">
         <v>36</v>
       </c>
       <c r="I2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L2" s="11"/>
       <c r="N2" t="s">
@@ -1580,60 +1710,169 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:N23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="13.42578125" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="16.28515625" customWidth="1"/>
+    <col min="1" max="1" width="23.42578125" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" customWidth="1"/>
+    <col min="3" max="3" width="23.85546875" customWidth="1"/>
+    <col min="4" max="4" width="22.140625" customWidth="1"/>
+    <col min="5" max="5" width="43.42578125" customWidth="1"/>
     <col min="6" max="6" width="12.7109375" customWidth="1"/>
     <col min="8" max="8" width="14.85546875" customWidth="1"/>
     <col min="10" max="10" width="14.140625" customWidth="1"/>
     <col min="11" max="11" width="18.140625" customWidth="1"/>
-    <col min="12" max="12" width="16" customWidth="1"/>
-    <col min="13" max="13" width="26.140625" customWidth="1"/>
+    <col min="12" max="13" width="16" customWidth="1"/>
+    <col min="14" max="14" width="26.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>48</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>51</v>
-      </c>
       <c r="K1" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>91</v>
-      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E2" t="s">
+        <v>127</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="I2" t="s">
+        <v>131</v>
+      </c>
+      <c r="K2" t="s">
+        <v>130</v>
+      </c>
+      <c r="M2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E3" t="s">
+        <v>70</v>
+      </c>
+      <c r="F3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G3" s="2"/>
+      <c r="M3" t="s">
+        <v>133</v>
+      </c>
+      <c r="N3" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G4" s="2"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G5" s="2"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G6" s="2"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G7" s="2"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G8" s="2"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G9" s="2"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G10" s="2"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G11" s="2"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G12" s="2"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G13" s="2"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G14" s="2"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G15" s="2"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G16" s="2"/>
+    </row>
+    <row r="17" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G17" s="2"/>
+    </row>
+    <row r="18" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G18" s="2"/>
+    </row>
+    <row r="19" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G19" s="2"/>
+    </row>
+    <row r="20" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G20" s="2"/>
+    </row>
+    <row r="21" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G21" s="2"/>
+    </row>
+    <row r="22" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G22" s="2"/>
+    </row>
+    <row r="23" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G23" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1643,9 +1882,637 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+  <dimension ref="A1:L36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="7.7109375" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="24.5703125" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D3" t="s">
+        <v>107</v>
+      </c>
+      <c r="E3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D4" t="s">
+        <v>101</v>
+      </c>
+      <c r="E4" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>94</v>
+      </c>
+      <c r="B5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D5" t="s">
+        <v>102</v>
+      </c>
+      <c r="E5" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>94</v>
+      </c>
+      <c r="B6" t="s">
+        <v>99</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D6" t="s">
+        <v>103</v>
+      </c>
+      <c r="E6" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>94</v>
+      </c>
+      <c r="B7" t="s">
+        <v>104</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="D7" t="s">
+        <v>105</v>
+      </c>
+      <c r="E7" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>94</v>
+      </c>
+      <c r="B8" t="s">
+        <v>104</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="D8" t="s">
+        <v>106</v>
+      </c>
+      <c r="E8" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>94</v>
+      </c>
+      <c r="B9" t="s">
+        <v>104</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D9" t="s">
+        <v>108</v>
+      </c>
+      <c r="E9" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>94</v>
+      </c>
+      <c r="B10" t="s">
+        <v>104</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D10" t="s">
+        <v>103</v>
+      </c>
+      <c r="E10" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>94</v>
+      </c>
+      <c r="B11" t="s">
+        <v>87</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D11" t="s">
+        <v>110</v>
+      </c>
+      <c r="E11" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>94</v>
+      </c>
+      <c r="B12" t="s">
+        <v>87</v>
+      </c>
+      <c r="C12" t="s">
+        <v>52</v>
+      </c>
+      <c r="D12" t="s">
+        <v>106</v>
+      </c>
+      <c r="E12" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>94</v>
+      </c>
+      <c r="B13" t="s">
+        <v>87</v>
+      </c>
+      <c r="C13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D13" t="s">
+        <v>111</v>
+      </c>
+      <c r="E13" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>94</v>
+      </c>
+      <c r="B14" t="s">
+        <v>87</v>
+      </c>
+      <c r="C14" t="s">
+        <v>55</v>
+      </c>
+      <c r="D14" t="s">
+        <v>108</v>
+      </c>
+      <c r="E14" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>94</v>
+      </c>
+      <c r="B15" t="s">
+        <v>87</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D15" t="s">
+        <v>103</v>
+      </c>
+      <c r="E15" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>94</v>
+      </c>
+      <c r="B16" t="s">
+        <v>89</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" t="s">
+        <v>110</v>
+      </c>
+      <c r="E16" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>94</v>
+      </c>
+      <c r="B17" t="s">
+        <v>89</v>
+      </c>
+      <c r="C17" t="s">
+        <v>52</v>
+      </c>
+      <c r="D17" t="s">
+        <v>106</v>
+      </c>
+      <c r="E17" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>94</v>
+      </c>
+      <c r="B18" t="s">
+        <v>89</v>
+      </c>
+      <c r="C18" t="s">
+        <v>49</v>
+      </c>
+      <c r="D18" t="s">
+        <v>111</v>
+      </c>
+      <c r="E18" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>94</v>
+      </c>
+      <c r="B19" t="s">
+        <v>89</v>
+      </c>
+      <c r="C19" t="s">
+        <v>55</v>
+      </c>
+      <c r="D19" t="s">
+        <v>108</v>
+      </c>
+      <c r="E19" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>94</v>
+      </c>
+      <c r="B20" t="s">
+        <v>89</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D20" t="s">
+        <v>103</v>
+      </c>
+      <c r="E20" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>94</v>
+      </c>
+      <c r="B21" t="s">
+        <v>113</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D21" t="s">
+        <v>110</v>
+      </c>
+      <c r="E21" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>94</v>
+      </c>
+      <c r="B22" t="s">
+        <v>113</v>
+      </c>
+      <c r="C22" t="s">
+        <v>52</v>
+      </c>
+      <c r="D22" t="s">
+        <v>106</v>
+      </c>
+      <c r="E22" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>94</v>
+      </c>
+      <c r="B23" t="s">
+        <v>113</v>
+      </c>
+      <c r="C23" t="s">
+        <v>49</v>
+      </c>
+      <c r="D23" t="s">
+        <v>111</v>
+      </c>
+      <c r="E23" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>94</v>
+      </c>
+      <c r="B24" t="s">
+        <v>113</v>
+      </c>
+      <c r="C24" t="s">
+        <v>55</v>
+      </c>
+      <c r="D24" t="s">
+        <v>108</v>
+      </c>
+      <c r="E24" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>94</v>
+      </c>
+      <c r="B25" t="s">
+        <v>113</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D25" t="s">
+        <v>103</v>
+      </c>
+      <c r="E25" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>94</v>
+      </c>
+      <c r="B26" t="s">
+        <v>90</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D26" t="s">
+        <v>110</v>
+      </c>
+      <c r="E26" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>94</v>
+      </c>
+      <c r="B27" t="s">
+        <v>90</v>
+      </c>
+      <c r="C27" t="s">
+        <v>52</v>
+      </c>
+      <c r="D27" t="s">
+        <v>106</v>
+      </c>
+      <c r="E27" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>94</v>
+      </c>
+      <c r="B28" t="s">
+        <v>90</v>
+      </c>
+      <c r="C28" t="s">
+        <v>49</v>
+      </c>
+      <c r="D28" t="s">
+        <v>111</v>
+      </c>
+      <c r="E28" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>94</v>
+      </c>
+      <c r="B29" t="s">
+        <v>90</v>
+      </c>
+      <c r="C29" t="s">
+        <v>55</v>
+      </c>
+      <c r="D29" t="s">
+        <v>108</v>
+      </c>
+      <c r="E29" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>94</v>
+      </c>
+      <c r="B30" t="s">
+        <v>90</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D30" t="s">
+        <v>103</v>
+      </c>
+      <c r="E30" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>94</v>
+      </c>
+      <c r="B31" t="s">
+        <v>90</v>
+      </c>
+      <c r="C31" t="s">
+        <v>80</v>
+      </c>
+      <c r="D31" t="s">
+        <v>114</v>
+      </c>
+      <c r="E31" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>94</v>
+      </c>
+      <c r="B32" t="s">
+        <v>126</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D32" t="s">
+        <v>110</v>
+      </c>
+      <c r="E32" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>94</v>
+      </c>
+      <c r="B33" t="s">
+        <v>126</v>
+      </c>
+      <c r="C33" t="s">
+        <v>52</v>
+      </c>
+      <c r="D33" t="s">
+        <v>106</v>
+      </c>
+      <c r="E33" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>94</v>
+      </c>
+      <c r="B34" t="s">
+        <v>126</v>
+      </c>
+      <c r="C34" t="s">
+        <v>49</v>
+      </c>
+      <c r="D34" t="s">
+        <v>111</v>
+      </c>
+      <c r="E34" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>94</v>
+      </c>
+      <c r="B35" t="s">
+        <v>126</v>
+      </c>
+      <c r="C35" t="s">
+        <v>55</v>
+      </c>
+      <c r="D35" t="s">
+        <v>108</v>
+      </c>
+      <c r="E35" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>94</v>
+      </c>
+      <c r="B36" t="s">
+        <v>126</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D36" t="s">
+        <v>103</v>
+      </c>
+      <c r="E36" t="s">
+        <v>119</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
 </worksheet>
 </file>
--- a/ver2/tree.xlsx
+++ b/ver2/tree.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="136">
   <si>
     <t>sex</t>
   </si>
@@ -436,6 +436,9 @@
   </si>
   <si>
     <t>Ульяновск_ Ленина_70-2020хх.png</t>
+  </si>
+  <si>
+    <t>Ульянов_Владимир_Ильич ; Свердлов_Яков_Михайлович</t>
   </si>
 </sst>
 </file>
@@ -1798,7 +1801,7 @@
         <v>132</v>
       </c>
       <c r="C3" t="s">
-        <v>63</v>
+        <v>135</v>
       </c>
       <c r="E3" t="s">
         <v>70</v>
